--- a/data/trans_orig/P33B1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023</t>
+          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36281</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22191</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39645</t>
+          <t>37743</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42685</t>
+          <t>42704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>69405</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44024</t>
+          <t>43757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49003</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75819</t>
+          <t>76602</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77361</t>
+          <t>76634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111874</t>
+          <t>112010</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81962</t>
+          <t>82514</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>112222</t>
+          <t>111858</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>166832</t>
+          <t>167188</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>211795</t>
+          <t>214119</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>335138</t>
+          <t>331675</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>375335</t>
+          <t>375069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273614</t>
+          <t>272897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>308010</t>
+          <t>307412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>618454</t>
+          <t>619562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>674146</t>
+          <t>672678</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>36569</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24464</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45992</t>
+          <t>46857</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>72517</t>
+          <t>71398</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37890</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25687</t>
+          <t>25956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47056</t>
+          <t>46057</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>46760</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77775</t>
+          <t>76814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76361</t>
+          <t>76325</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109826</t>
+          <t>109400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75657</t>
+          <t>75432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102477</t>
+          <t>101533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158848</t>
+          <t>160372</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>201764</t>
+          <t>204166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>290779</t>
+          <t>288544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>329623</t>
+          <t>329483</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211888</t>
+          <t>212393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>243675</t>
+          <t>243722</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>510785</t>
+          <t>510242</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562488</t>
+          <t>562735</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64814</t>
+          <t>67784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>15232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27529</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89004</t>
+          <t>87721</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61836</t>
+          <t>64438</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33034</t>
+          <t>33036</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>91555</t>
+          <t>89720</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>32353</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135160</t>
+          <t>136863</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32099</t>
+          <t>32212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49261</t>
+          <t>48165</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49074</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178838</t>
+          <t>175985</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413357</t>
+          <t>411403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>611808</t>
+          <t>603344</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71476</t>
+          <t>72068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>92618</t>
+          <t>91952</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>487712</t>
+          <t>489267</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>739528</t>
+          <t>723985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>86,75%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63037</t>
+          <t>63206</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>93196</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>36528</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>94671</t>
+          <t>91861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106174</t>
+          <t>97371</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174079</t>
+          <t>172751</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45620</t>
+          <t>43534</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72264</t>
+          <t>70854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97587</t>
+          <t>98344</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91505</t>
+          <t>86573</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154724</t>
+          <t>151822</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>191961</t>
+          <t>191044</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>246284</t>
+          <t>246558</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>90641</t>
+          <t>100085</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>230337</t>
+          <t>230731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>285324</t>
+          <t>279091</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>449937</t>
+          <t>450893</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>649007</t>
+          <t>651492</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>716239</t>
+          <t>712872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>566637</t>
+          <t>568457</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>816117</t>
+          <t>792295</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1255195</t>
+          <t>1257395</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1530331</t>
+          <t>1559115</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23746</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44165</t>
+          <t>45638</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>76000</t>
+          <t>75189</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>121611</t>
+          <t>122405</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109334</t>
+          <t>104513</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>156460</t>
+          <t>155734</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>25416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47923</t>
+          <t>46868</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72674</t>
+          <t>72766</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>117013</t>
+          <t>116010</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108467</t>
+          <t>106620</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154497</t>
+          <t>154255</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76869</t>
+          <t>76857</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111551</t>
+          <t>115800</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>136980</t>
+          <t>140485</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214081</t>
+          <t>218798</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>227885</t>
+          <t>231302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>313131</t>
+          <t>314018</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>289913</t>
+          <t>288865</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>332161</t>
+          <t>334391</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>401680</t>
+          <t>397672</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>562091</t>
+          <t>544460</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>717650</t>
+          <t>716496</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>872021</t>
+          <t>877818</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5649</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90671</t>
+          <t>90468</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122233</t>
+          <t>121796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102480</t>
+          <t>102026</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140656</t>
+          <t>140206</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22496</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65162</t>
+          <t>65205</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>91926</t>
+          <t>93002</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71682</t>
+          <t>70537</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>103580</t>
+          <t>106017</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12540</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>42270</t>
+          <t>45265</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>164883</t>
+          <t>164610</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>204532</t>
+          <t>203711</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>184292</t>
+          <t>185810</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>232174</t>
+          <t>235340</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>172223</t>
+          <t>171914</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>210989</t>
+          <t>209940</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>367247</t>
+          <t>369468</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>418604</t>
+          <t>418658</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>553097</t>
+          <t>548609</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>618111</t>
+          <t>623790</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,26%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>162588</t>
+          <t>161299</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>243990</t>
+          <t>243089</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>295456</t>
+          <t>292378</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>398132</t>
+          <t>396457</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>498628</t>
+          <t>490588</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>628762</t>
+          <t>626313</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>146213</t>
+          <t>150719</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>224134</t>
+          <t>226269</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>274535</t>
+          <t>275678</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>373204</t>
+          <t>375770</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>460617</t>
+          <t>449407</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>581592</t>
+          <t>581254</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>463451</t>
+          <t>479444</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>669212</t>
+          <t>665964</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>623224</t>
+          <t>638279</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>842345</t>
+          <t>842650</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1187907</t>
+          <t>1156238</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1484458</t>
+          <t>1476438</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2268616</t>
+          <t>2267481</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2586898</t>
+          <t>2574207</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1988571</t>
+          <t>1991155</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2420173</t>
+          <t>2362560</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4297238</t>
+          <t>4302493</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4789680</t>
+          <t>4874870</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>70,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>26264</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35208</t>
+          <t>39368</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>32975</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22271</t>
+          <t>24541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37743</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54135</t>
+          <t>59239</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42704</t>
+          <t>46073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69405</t>
+          <t>75860</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31117</t>
+          <t>32793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>22877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43757</t>
+          <t>44215</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30601</t>
+          <t>33779</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>25851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>43529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>66572</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49725</t>
+          <t>53059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76602</t>
+          <t>82291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>93037</t>
+          <t>103067</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76634</t>
+          <t>84403</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112010</t>
+          <t>123770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95983</t>
+          <t>107462</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>82514</t>
+          <t>92262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>111858</t>
+          <t>124574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>189019</t>
+          <t>210530</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>167188</t>
+          <t>189444</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>214119</t>
+          <t>235868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>356724</t>
+          <t>388494</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>331675</t>
+          <t>366779</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>375069</t>
+          <t>409536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>291083</t>
+          <t>314195</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272897</t>
+          <t>294408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>307412</t>
+          <t>330900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>647807</t>
+          <t>702689</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>619562</t>
+          <t>671251</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>672678</t>
+          <t>727946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25855</t>
+          <t>27952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18228</t>
+          <t>19136</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>36569</t>
+          <t>39441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32209</t>
+          <t>36362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23896</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41848</t>
+          <t>48570</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>64315</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>50644</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>71398</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38867</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34519</t>
+          <t>38576</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25956</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46057</t>
+          <t>51188</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,22 +1477,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59416</t>
+          <t>64044</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>50746</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76814</t>
+          <t>79556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92161</t>
+          <t>100702</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76325</t>
+          <t>85448</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>109400</t>
+          <t>120193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88215</t>
+          <t>97659</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75432</t>
+          <t>83152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>112040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>180376</t>
+          <t>198360</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>174565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204166</t>
+          <t>222076</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>309300</t>
+          <t>329090</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>288544</t>
+          <t>304936</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>329483</t>
+          <t>347572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>227637</t>
+          <t>250545</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212393</t>
+          <t>232992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>243722</t>
+          <t>267734</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>536937</t>
+          <t>579635</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>510242</t>
+          <t>552036</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>562735</t>
+          <t>606929</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,96%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38395</t>
+          <t>40961</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>30713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>67784</t>
+          <t>52731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20977</t>
+          <t>23811</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>31186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>59372</t>
+          <t>64771</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>26666</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>87721</t>
+          <t>79871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36207</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>26191</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64438</t>
+          <t>51597</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23534</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16514</t>
+          <t>17865</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33036</t>
+          <t>37431</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>59741</t>
+          <t>64082</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23291</t>
+          <t>49443</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>89720</t>
+          <t>79452</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>81686</t>
+          <t>94109</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>78192</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136863</t>
+          <t>111615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>39685</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>34351</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48165</t>
+          <t>52676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>121371</t>
+          <t>137048</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>119600</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175985</t>
+          <t>157588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>511976</t>
+          <t>298615</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>411403</t>
+          <t>276255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>603344</t>
+          <t>319679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>82149</t>
+          <t>94025</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72068</t>
+          <t>83265</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91952</t>
+          <t>105297</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>594125</t>
+          <t>392639</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>489267</t>
+          <t>368089</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>723985</t>
+          <t>416072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166345</t>
+          <t>186929</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834609</t>
+          <t>658540</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>77682</t>
+          <t>87272</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63206</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93196</t>
+          <t>105862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68663</t>
+          <t>76383</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36528</t>
+          <t>61641</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>92004</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>146345</t>
+          <t>163656</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97371</t>
+          <t>143543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>172751</t>
+          <t>186058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>57056</t>
+          <t>60657</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>47540</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70854</t>
+          <t>75515</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>72056</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>38268</t>
+          <t>70782</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98344</t>
+          <t>98359</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>129111</t>
+          <t>144576</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>86573</t>
+          <t>123885</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>151822</t>
+          <t>164353</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>218191</t>
+          <t>239156</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>191044</t>
+          <t>211400</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>246558</t>
+          <t>269212</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>175773</t>
+          <t>195497</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>100085</t>
+          <t>175163</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>230731</t>
+          <t>217846</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>393964</t>
+          <t>434653</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>279091</t>
+          <t>401966</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>450893</t>
+          <t>469521</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>681890</t>
+          <t>744758</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>651492</t>
+          <t>709701</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>712872</t>
+          <t>778765</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>661603</t>
+          <t>505411</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>568457</t>
+          <t>478808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>792295</t>
+          <t>531033</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1343492</t>
+          <t>1250169</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1257395</t>
+          <t>1210170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1559115</t>
+          <t>1292089</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>64,83%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32508</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>25567</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>45638</t>
+          <t>47064</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>101119</t>
+          <t>116138</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75189</t>
+          <t>100877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>122405</t>
+          <t>135278</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>133628</t>
+          <t>152105</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>104513</t>
+          <t>132752</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>155734</t>
+          <t>172459</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25416</t>
+          <t>28319</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>52595</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>106731</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72766</t>
+          <t>91515</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116010</t>
+          <t>121313</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>133468</t>
+          <t>146485</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>106620</t>
+          <t>127182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>154255</t>
+          <t>165327</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>94300</t>
+          <t>110671</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76857</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>115800</t>
+          <t>131232</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>187407</t>
+          <t>210290</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140485</t>
+          <t>191830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>218798</t>
+          <t>233255</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>281707</t>
+          <t>320961</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231302</t>
+          <t>294691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>314018</t>
+          <t>352391</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>311672</t>
+          <t>380490</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>288865</t>
+          <t>355836</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>334391</t>
+          <t>403697</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>452537</t>
+          <t>396969</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>397672</t>
+          <t>371607</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>544460</t>
+          <t>420987</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>764209</t>
+          <t>777458</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>716496</t>
+          <t>744054</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>877818</t>
+          <t>812244</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>58,14%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>14226</t>
+          <t>12926</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>29720</t>
+          <t>29828</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,27 +3605,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>105958</t>
+          <t>117944</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90468</t>
+          <t>100404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>121796</t>
+          <t>135056</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>120183</t>
+          <t>130871</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102026</t>
+          <t>110021</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140206</t>
+          <t>153810</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3075</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22324</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77909</t>
+          <t>86672</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65205</t>
+          <t>72595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93002</t>
+          <t>105671</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>86603</t>
+          <t>96360</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>70537</t>
+          <t>80852</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106017</t>
+          <t>117867</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>22940</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>45265</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>184023</t>
+          <t>205823</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>164610</t>
+          <t>185357</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>203711</t>
+          <t>231723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>207805</t>
+          <t>228763</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>185810</t>
+          <t>202786</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>235340</t>
+          <t>254291</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>193805</t>
+          <t>191674</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>171914</t>
+          <t>169024</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>209940</t>
+          <t>206741</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>393481</t>
+          <t>433841</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>369468</t>
+          <t>406609</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>418658</t>
+          <t>462666</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>587286</t>
+          <t>625515</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>548609</t>
+          <t>590228</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>623790</t>
+          <t>660752</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>213001</t>
+          <t>231343</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>161299</t>
+          <t>202307</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>243089</t>
+          <t>263174</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>358726</t>
+          <t>403613</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>292378</t>
+          <t>372695</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>396457</t>
+          <t>436560</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>571728</t>
+          <t>634956</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>490588</t>
+          <t>593828</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>626313</t>
+          <t>677131</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>193506</t>
+          <t>206287</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>150719</t>
+          <t>180817</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>226269</t>
+          <t>239321</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>336551</t>
+          <t>375832</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>275678</t>
+          <t>347606</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>375770</t>
+          <t>409434</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>530057</t>
+          <t>582119</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>449407</t>
+          <t>539333</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>581254</t>
+          <t>623818</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>603157</t>
+          <t>670645</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>479444</t>
+          <t>622393</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>665964</t>
+          <t>715984</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>771085</t>
+          <t>859670</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>638279</t>
+          <t>819188</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>842650</t>
+          <t>908403</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1374242</t>
+          <t>1530315</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1156238</t>
+          <t>1461997</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1476438</t>
+          <t>1595963</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2365367</t>
+          <t>2333119</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2267481</t>
+          <t>2270406</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2574207</t>
+          <t>2385249</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2108490</t>
+          <t>1994986</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1991155</t>
+          <t>1939806</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2362560</t>
+          <t>2044612</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4473857</t>
+          <t>4328105</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4302493</t>
+          <t>4248428</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4874870</t>
+          <t>4410043</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3375031</t>
+          <t>3441394</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3574853</t>
+          <t>3634102</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3574853</t>
+          <t>3634102</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3574853</t>
+          <t>3634102</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6949884</t>
+          <t>7075496</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6949884</t>
+          <t>7075496</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6949884</t>
+          <t>7075496</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
